--- a/data/trans_orig/P33_MIN_2023_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33_MIN_2023_R-Estudios-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nº medio de minutos durante los cuales la población se echa la siesta</t>
+          <t>Nº medio de minutos durante los cuales la población se echa la siesta (tasa de respuesta: 37,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,9; 47,11</t>
+          <t>38,7; 47,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,83; 44,29</t>
+          <t>37,44; 44,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,19; 44,48</t>
+          <t>39,16; 44,58</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,47; 40,48</t>
+          <t>13,33; 40,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,96; 39,2</t>
+          <t>12,0; 39,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,94; 38,52</t>
+          <t>16,77; 38,52</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,4; 35,51</t>
+          <t>25,19; 35,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,67; 41,51</t>
+          <t>23,43; 42,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,3; 36,04</t>
+          <t>25,96; 35,51</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,99; 39,24</t>
+          <t>19,07; 39,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,27; 38,34</t>
+          <t>19,59; 38,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,71; 37,92</t>
+          <t>23,23; 37,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_MIN_2023_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33_MIN_2023_R-Estudios-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>42,98</t>
+          <t>43,03</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40,75</t>
+          <t>41,11</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41,8</t>
+          <t>42,01</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,7; 47,35</t>
+          <t>39,06; 47,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,44; 44,17</t>
+          <t>37,55; 44,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,16; 44,58</t>
+          <t>39,23; 44,85</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29,04</t>
+          <t>39,61</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27,33</t>
+          <t>37,91</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28,29</t>
+          <t>38,87</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,33; 40,55</t>
+          <t>36,18; 43,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,0; 39,41</t>
+          <t>34,49; 41,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,77; 38,52</t>
+          <t>36,37; 41,6</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>29,99</t>
+          <t>29,83</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>29,63</t>
+          <t>30,12</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29,83</t>
+          <t>29,96</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,19; 35,02</t>
+          <t>25,03; 35,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,43; 42,22</t>
+          <t>24,76; 43,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,96; 35,51</t>
+          <t>26,54; 35,12</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>32,15</t>
+          <t>38,47</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31,44</t>
+          <t>37,47</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31,83</t>
+          <t>38,01</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 39,26</t>
+          <t>35,99; 40,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,59; 38,08</t>
+          <t>35,1; 40,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,23; 37,67</t>
+          <t>36,42; 39,72</t>
         </is>
       </c>
     </row>
